--- a/Assessment Questions/AIE/DBM-120/SQL Commands and Clauses/Select, Select distinct/Select_Clauses.xlsx
+++ b/Assessment Questions/AIE/DBM-120/SQL Commands and Clauses/Select, Select distinct/Select_Clauses.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Select &amp; Distinct" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,356 +413,456 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>COMMON DATASET (MySQL)</t>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Option D</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Employees(emp_id, emp_name, age, salary, dept_id, joining_date)</t>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Select_Clauses</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>A company wants to generate a detailed employee report. Write a SQL query using Select &amp; Distinct to retrieve all employee details along with department names.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Departments(dept_id, dept_name)</t>
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Select_Clauses</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Write a query using Select &amp; Distinct to retrieve distinct department IDs from Employees table.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Projects(project_id, project_name, dept_id)</t>
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Select_Clauses</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A manager wants to display employee names as 'Employee Name'. Write a query using Select &amp; Distinct with aliases.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Assignments(emp_id, project_id, hours_worked)</t>
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Select_Clauses</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Write a query using Select &amp; Distinct to find employees whose salary is greater than 50000 and belong to dept_id = 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Select_Clauses</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Using Select &amp; Distinct, retrieve employees whose salary lies between 40000 and 70000.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Q.No</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Select_Clauses</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scenario-Based SQL Question</t>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Write a query using Select &amp; Distinct to display employees sorted by salary in descending order.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Select_Clauses</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A company wants to generate a detailed employee report. Write a SQL query using Select &amp; Distinct to retrieve all employee details along with department names.</t>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Using Select &amp; Distinct, retrieve employees whose department is in (1,2,3).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Select_Clauses</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Write a query using Select &amp; Distinct to retrieve distinct department IDs from Employees table.</t>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Write a query using Select &amp; Distinct to find employees whose names start with 'A'.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Select_Clauses</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A manager wants to display employee names as 'Employee Name'. Write a query using Select &amp; Distinct with aliases.</t>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Using Select &amp; Distinct, limit the output to top 5 highest paid employees.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Select_Clauses</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Write a query using Select &amp; Distinct to find employees whose salary is greater than 50000 and belong to dept_id = 1.</t>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Write a query using Select &amp; Distinct to find employees with NULL manager_id.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Select_Clauses</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Using Select &amp; Distinct, retrieve employees whose salary lies between 40000 and 70000.</t>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Using Select &amp; Distinct, group employees by department and calculate average salary.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Select_Clauses</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Write a query using Select &amp; Distinct to display employees sorted by salary in descending order.</t>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Write a query using Select &amp; Distinct to find departments having more than 3 employees.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Select_Clauses</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Using Select &amp; Distinct, retrieve employees whose department is in (1,2,3).</t>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Using Select &amp; Distinct, find employees whose salary is greater than average salary using subquery.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Select_Clauses</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Write a query using Select &amp; Distinct to find employees whose names start with 'A'.</t>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Write a query using Select &amp; Distinct to find employees working in departments with highest salary.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Select_Clauses</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Using Select &amp; Distinct, limit the output to top 5 highest paid employees.</t>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Using Select &amp; Distinct, retrieve employees who are not assigned to any project.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Select_Clauses</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Write a query using Select &amp; Distinct to find employees with NULL manager_id.</t>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Write a query using Select &amp; Distinct to calculate total hours worked per employee.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Select_Clauses</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Using Select &amp; Distinct, group employees by department and calculate average salary.</t>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Using Select &amp; Distinct, find employees whose salary is within top 10% in company.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Select_Clauses</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Write a query using Select &amp; Distinct to find departments having more than 3 employees.</t>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Write a query using Select &amp; Distinct to list departments with total salary greater than 200000.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Select_Clauses</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Using Select &amp; Distinct, find employees whose salary is greater than average salary using subquery.</t>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Using Select &amp; Distinct, find employees working on multiple projects.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Select_Clauses</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Write a query using Select &amp; Distinct to find employees working in departments with highest salary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>15</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Using Select &amp; Distinct, retrieve employees who are not assigned to any project.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>16</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Write a query using Select &amp; Distinct to calculate total hours worked per employee.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>17</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Using Select &amp; Distinct, find employees whose salary is within top 10% in company.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>18</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Write a query using Select &amp; Distinct to list departments with total salary greater than 200000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>19</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Using Select &amp; Distinct, find employees working on multiple projects.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>20</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Write a query using Select &amp; Distinct to retrieve employees along with department and project details.</t>
         </is>
